--- a/顔.xlsx
+++ b/顔.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\ssd1360\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135F12EB-6665-4D36-B852-5F09FA132C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C59B5D-E464-4C55-949D-ED0812E11F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
     <sheet name="通常" sheetId="2" r:id="rId2"/>
+    <sheet name="驚き" sheetId="3" r:id="rId3"/>
+    <sheet name="EX" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -432,6 +434,847 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>142895</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="グループ化 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC33ED6E-E564-4659-9673-653925334741}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="14168437" y="11787187"/>
+          <a:ext cx="2476500" cy="738208"/>
+          <a:chOff x="14168437" y="12739667"/>
+          <a:chExt cx="2476500" cy="738208"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="3" name="直線コネクタ 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4A199E-C5BE-E031-AFC7-D26AEC2D96B2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="14168437" y="12763480"/>
+            <a:ext cx="1190625" cy="714395"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="190500"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="4" name="直線コネクタ 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB896C6F-FDB7-F354-C586-DA42AB46137D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="15430500" y="12739667"/>
+            <a:ext cx="1214437" cy="738208"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="190500"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>23818</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95255</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3E01E5B-CFD2-4F1A-8D3C-77AF0F470B9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9715500" y="2405068"/>
+          <a:ext cx="0" cy="3643312"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>88</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>23814</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>88</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91254E2-51D1-4EAE-9145-0A7B4BE7FDD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21145501" y="2405064"/>
+          <a:ext cx="0" cy="3643312"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2F47ECA-9001-4CAA-8339-B9736F3512A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8439150" y="4152905"/>
+          <a:ext cx="2657475" cy="14282"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>83</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>94</xdr:col>
+      <xdr:colOff>119062</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{498CC741-9FD7-4213-A0CE-4660A83635A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="19892962" y="4152905"/>
+          <a:ext cx="2657475" cy="14282"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>80982</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>119062</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1771A374-E7D2-4997-994E-8F995CAAF5D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15368587" y="7939107"/>
+          <a:ext cx="1228725" cy="3871893"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>19070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>214312</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0E143FE-BFC2-46EB-91AB-81772ACF3BBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="14192250" y="7877195"/>
+          <a:ext cx="1114425" cy="4005242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>142895</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="グループ化 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7BDF5F7-2A4A-494C-8935-0803E9350A0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="14168437" y="11787187"/>
+          <a:ext cx="2476500" cy="738208"/>
+          <a:chOff x="14168437" y="12739667"/>
+          <a:chExt cx="2476500" cy="738208"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="3" name="直線コネクタ 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA12307-76C1-17CA-1179-41B02E5DA9C5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="14168437" y="12763480"/>
+            <a:ext cx="1190625" cy="714395"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="190500"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="4" name="直線コネクタ 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{777BB037-785D-A6F2-E917-CBC00786B84B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="15430500" y="12739667"/>
+            <a:ext cx="1214437" cy="738208"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="190500"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>166692</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED03AA43-4E2C-46E3-B1C2-A7740753F5BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9834562" y="2738437"/>
+          <a:ext cx="1976438" cy="1476380"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>80982</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>119062</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9EA4876-EA23-4910-B028-8FAE9C608276}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15368587" y="7939107"/>
+          <a:ext cx="1228725" cy="3871893"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>19070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>214312</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AA80E1F-2948-41CC-B336-12B9699AE63F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="14192250" y="7877195"/>
+          <a:ext cx="1114425" cy="4005242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>119062</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7346B6D5-3A4F-4D61-B24E-5BC4EF19E569}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9906000" y="4214812"/>
+          <a:ext cx="1928812" cy="1452563"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="190500"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>79</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>87</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="20" name="グループ化 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B678078D-26F6-30AF-DA4B-248D1BD10876}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm flipH="1">
+          <a:off x="18916650" y="2700337"/>
+          <a:ext cx="2000250" cy="2928938"/>
+          <a:chOff x="11153775" y="4057649"/>
+          <a:chExt cx="2000250" cy="2928938"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="18" name="直線コネクタ 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433BEAF6-ECDF-469F-8435-C21B98C0A4D6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11153775" y="4057649"/>
+            <a:ext cx="1976438" cy="1476380"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="190500"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="19" name="直線コネクタ 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3615B0B5-FF53-4C4E-95D3-14717408B78A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="11225213" y="5534024"/>
+            <a:ext cx="1928812" cy="1452563"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="190500"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4912,4 +5755,4228 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63DE6B66-0A82-4603-881A-1346C50DFF55}">
+  <dimension ref="A1:DZ66"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="3.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:130">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2">
+        <v>18</v>
+      </c>
+      <c r="U1" s="2">
+        <v>19</v>
+      </c>
+      <c r="V1" s="2">
+        <v>20</v>
+      </c>
+      <c r="W1" s="2">
+        <v>21</v>
+      </c>
+      <c r="X1" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="2">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="2">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="2">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="2">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="2">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="2">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="2">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="2">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="2">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="2">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="2">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="2">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="2">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="2">
+        <v>52</v>
+      </c>
+      <c r="BC1" s="2">
+        <v>53</v>
+      </c>
+      <c r="BD1" s="2">
+        <v>54</v>
+      </c>
+      <c r="BE1" s="2">
+        <v>55</v>
+      </c>
+      <c r="BF1" s="2">
+        <v>56</v>
+      </c>
+      <c r="BG1" s="2">
+        <v>57</v>
+      </c>
+      <c r="BH1" s="2">
+        <v>58</v>
+      </c>
+      <c r="BI1" s="2">
+        <v>59</v>
+      </c>
+      <c r="BJ1" s="2">
+        <v>60</v>
+      </c>
+      <c r="BK1" s="2">
+        <v>61</v>
+      </c>
+      <c r="BL1" s="2">
+        <v>62</v>
+      </c>
+      <c r="BM1" s="3">
+        <v>63</v>
+      </c>
+      <c r="BN1" s="2">
+        <v>64</v>
+      </c>
+      <c r="BO1" s="2">
+        <v>65</v>
+      </c>
+      <c r="BP1" s="2">
+        <v>66</v>
+      </c>
+      <c r="BQ1" s="2">
+        <v>67</v>
+      </c>
+      <c r="BR1" s="2">
+        <v>68</v>
+      </c>
+      <c r="BS1" s="2">
+        <v>69</v>
+      </c>
+      <c r="BT1" s="2">
+        <v>70</v>
+      </c>
+      <c r="BU1" s="2">
+        <v>71</v>
+      </c>
+      <c r="BV1" s="2">
+        <v>72</v>
+      </c>
+      <c r="BW1" s="2">
+        <v>73</v>
+      </c>
+      <c r="BX1" s="2">
+        <v>74</v>
+      </c>
+      <c r="BY1" s="2">
+        <v>75</v>
+      </c>
+      <c r="BZ1" s="2">
+        <v>76</v>
+      </c>
+      <c r="CA1" s="2">
+        <v>77</v>
+      </c>
+      <c r="CB1" s="3">
+        <v>78</v>
+      </c>
+      <c r="CC1" s="2">
+        <v>79</v>
+      </c>
+      <c r="CD1" s="2">
+        <v>80</v>
+      </c>
+      <c r="CE1" s="2">
+        <v>81</v>
+      </c>
+      <c r="CF1" s="2">
+        <v>82</v>
+      </c>
+      <c r="CG1" s="2">
+        <v>83</v>
+      </c>
+      <c r="CH1" s="2">
+        <v>84</v>
+      </c>
+      <c r="CI1" s="2">
+        <v>85</v>
+      </c>
+      <c r="CJ1" s="2">
+        <v>86</v>
+      </c>
+      <c r="CK1" s="2">
+        <v>87</v>
+      </c>
+      <c r="CL1" s="2">
+        <v>88</v>
+      </c>
+      <c r="CM1" s="2">
+        <v>89</v>
+      </c>
+      <c r="CN1" s="2">
+        <v>90</v>
+      </c>
+      <c r="CO1" s="2">
+        <v>91</v>
+      </c>
+      <c r="CP1" s="2">
+        <v>92</v>
+      </c>
+      <c r="CQ1" s="2">
+        <v>93</v>
+      </c>
+      <c r="CR1" s="2">
+        <v>94</v>
+      </c>
+      <c r="CS1" s="3">
+        <v>95</v>
+      </c>
+      <c r="CT1" s="2">
+        <v>96</v>
+      </c>
+      <c r="CU1" s="2">
+        <v>97</v>
+      </c>
+      <c r="CV1" s="2">
+        <v>98</v>
+      </c>
+      <c r="CW1" s="2">
+        <v>99</v>
+      </c>
+      <c r="CX1" s="2">
+        <v>100</v>
+      </c>
+      <c r="CY1" s="2">
+        <v>101</v>
+      </c>
+      <c r="CZ1" s="2">
+        <v>102</v>
+      </c>
+      <c r="DA1" s="2">
+        <v>103</v>
+      </c>
+      <c r="DB1" s="2">
+        <v>104</v>
+      </c>
+      <c r="DC1" s="2">
+        <v>105</v>
+      </c>
+      <c r="DD1" s="2">
+        <v>106</v>
+      </c>
+      <c r="DE1" s="2">
+        <v>107</v>
+      </c>
+      <c r="DF1" s="2">
+        <v>108</v>
+      </c>
+      <c r="DG1" s="2">
+        <v>109</v>
+      </c>
+      <c r="DH1" s="2">
+        <v>110</v>
+      </c>
+      <c r="DI1" s="3">
+        <v>111</v>
+      </c>
+      <c r="DJ1" s="2">
+        <v>112</v>
+      </c>
+      <c r="DK1" s="2">
+        <v>113</v>
+      </c>
+      <c r="DL1" s="2">
+        <v>114</v>
+      </c>
+      <c r="DM1" s="2">
+        <v>115</v>
+      </c>
+      <c r="DN1" s="2">
+        <v>116</v>
+      </c>
+      <c r="DO1" s="2">
+        <v>117</v>
+      </c>
+      <c r="DP1" s="2">
+        <v>118</v>
+      </c>
+      <c r="DQ1" s="2">
+        <v>119</v>
+      </c>
+      <c r="DR1" s="2">
+        <v>120</v>
+      </c>
+      <c r="DS1" s="2">
+        <v>121</v>
+      </c>
+      <c r="DT1" s="2">
+        <v>122</v>
+      </c>
+      <c r="DU1" s="2">
+        <v>123</v>
+      </c>
+      <c r="DV1" s="2">
+        <v>124</v>
+      </c>
+      <c r="DW1" s="2">
+        <v>125</v>
+      </c>
+      <c r="DX1" s="2">
+        <v>126</v>
+      </c>
+      <c r="DY1" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:130">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="BM2" s="6"/>
+      <c r="CB2" s="5"/>
+      <c r="CS2" s="5"/>
+      <c r="DI2" s="5"/>
+      <c r="DZ2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:130">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="BM3" s="6"/>
+      <c r="CB3" s="5"/>
+      <c r="CS3" s="5"/>
+      <c r="DI3" s="5"/>
+      <c r="DZ3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:130">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="BM4" s="6"/>
+      <c r="CB4" s="5"/>
+      <c r="CS4" s="5"/>
+      <c r="DI4" s="5"/>
+      <c r="DZ4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:130">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="BM5" s="6"/>
+      <c r="CB5" s="5"/>
+      <c r="CS5" s="5"/>
+      <c r="DI5" s="5"/>
+      <c r="DZ5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:130">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AX6" s="5"/>
+      <c r="BM6" s="6"/>
+      <c r="CB6" s="5"/>
+      <c r="CS6" s="5"/>
+      <c r="DI6" s="5"/>
+      <c r="DZ6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:130">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AX7" s="5"/>
+      <c r="BM7" s="6"/>
+      <c r="CB7" s="5"/>
+      <c r="CS7" s="5"/>
+      <c r="DI7" s="5"/>
+      <c r="DZ7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:130">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AX8" s="5"/>
+      <c r="BM8" s="6"/>
+      <c r="CB8" s="5"/>
+      <c r="CS8" s="5"/>
+      <c r="DI8" s="5"/>
+      <c r="DZ8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:130">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AX9" s="5"/>
+      <c r="BM9" s="6"/>
+      <c r="CB9" s="5"/>
+      <c r="CS9" s="5"/>
+      <c r="DI9" s="5"/>
+      <c r="DZ9" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:130">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AX10" s="5"/>
+      <c r="BM10" s="6"/>
+      <c r="CB10" s="5"/>
+      <c r="CS10" s="5"/>
+      <c r="DI10" s="5"/>
+      <c r="DZ10" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:130">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AX11" s="5"/>
+      <c r="BM11" s="6"/>
+      <c r="CB11" s="5"/>
+      <c r="CS11" s="5"/>
+      <c r="DI11" s="5"/>
+      <c r="DZ11" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:130">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AX12" s="5"/>
+      <c r="BM12" s="6"/>
+      <c r="CB12" s="5"/>
+      <c r="CS12" s="5"/>
+      <c r="DI12" s="5"/>
+      <c r="DZ12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:130">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AX13" s="5"/>
+      <c r="BM13" s="6"/>
+      <c r="CB13" s="5"/>
+      <c r="CS13" s="5"/>
+      <c r="DI13" s="5"/>
+      <c r="DZ13" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:130">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AX14" s="5"/>
+      <c r="BM14" s="6"/>
+      <c r="CB14" s="5"/>
+      <c r="CS14" s="5"/>
+      <c r="DI14" s="5"/>
+      <c r="DZ14" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:130">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AX15" s="5"/>
+      <c r="BM15" s="6"/>
+      <c r="CB15" s="5"/>
+      <c r="CS15" s="5"/>
+      <c r="DI15" s="5"/>
+      <c r="DZ15" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:130">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AX16" s="5"/>
+      <c r="BM16" s="6"/>
+      <c r="CB16" s="5"/>
+      <c r="CS16" s="5"/>
+      <c r="DI16" s="5"/>
+      <c r="DZ16" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:130">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="AG17" s="5"/>
+      <c r="AX17" s="5"/>
+      <c r="BM17" s="6"/>
+      <c r="CB17" s="5"/>
+      <c r="CS17" s="5"/>
+      <c r="DI17" s="5"/>
+      <c r="DZ17" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:130">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="5"/>
+      <c r="AS18" s="5"/>
+      <c r="AT18" s="5"/>
+      <c r="AU18" s="5"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="5"/>
+      <c r="AY18" s="5"/>
+      <c r="AZ18" s="5"/>
+      <c r="BA18" s="5"/>
+      <c r="BB18" s="5"/>
+      <c r="BC18" s="5"/>
+      <c r="BD18" s="5"/>
+      <c r="BE18" s="5"/>
+      <c r="BF18" s="5"/>
+      <c r="BG18" s="5"/>
+      <c r="BH18" s="5"/>
+      <c r="BI18" s="5"/>
+      <c r="BJ18" s="5"/>
+      <c r="BK18" s="5"/>
+      <c r="BL18" s="5"/>
+      <c r="BM18" s="6"/>
+      <c r="BN18" s="5"/>
+      <c r="BO18" s="5"/>
+      <c r="BP18" s="5"/>
+      <c r="BQ18" s="5"/>
+      <c r="BR18" s="5"/>
+      <c r="BS18" s="5"/>
+      <c r="BT18" s="5"/>
+      <c r="BU18" s="5"/>
+      <c r="BV18" s="5"/>
+      <c r="BW18" s="5"/>
+      <c r="BX18" s="5"/>
+      <c r="BY18" s="5"/>
+      <c r="BZ18" s="5"/>
+      <c r="CA18" s="5"/>
+      <c r="CB18" s="5"/>
+      <c r="CC18" s="5"/>
+      <c r="CD18" s="5"/>
+      <c r="CE18" s="5"/>
+      <c r="CF18" s="5"/>
+      <c r="CG18" s="5"/>
+      <c r="CH18" s="5"/>
+      <c r="CI18" s="5"/>
+      <c r="CJ18" s="5"/>
+      <c r="CK18" s="5"/>
+      <c r="CL18" s="5"/>
+      <c r="CM18" s="5"/>
+      <c r="CN18" s="5"/>
+      <c r="CO18" s="5"/>
+      <c r="CP18" s="5"/>
+      <c r="CQ18" s="5"/>
+      <c r="CR18" s="5"/>
+      <c r="CS18" s="5"/>
+      <c r="CT18" s="5"/>
+      <c r="CU18" s="5"/>
+      <c r="CV18" s="5"/>
+      <c r="CW18" s="5"/>
+      <c r="CX18" s="5"/>
+      <c r="CY18" s="5"/>
+      <c r="CZ18" s="5"/>
+      <c r="DA18" s="5"/>
+      <c r="DB18" s="5"/>
+      <c r="DC18" s="5"/>
+      <c r="DD18" s="5"/>
+      <c r="DE18" s="5"/>
+      <c r="DF18" s="5"/>
+      <c r="DG18" s="5"/>
+      <c r="DH18" s="5"/>
+      <c r="DI18" s="5"/>
+      <c r="DJ18" s="5"/>
+      <c r="DK18" s="5"/>
+      <c r="DL18" s="5"/>
+      <c r="DM18" s="5"/>
+      <c r="DN18" s="5"/>
+      <c r="DO18" s="5"/>
+      <c r="DP18" s="5"/>
+      <c r="DQ18" s="5"/>
+      <c r="DR18" s="5"/>
+      <c r="DS18" s="5"/>
+      <c r="DT18" s="5"/>
+      <c r="DU18" s="5"/>
+      <c r="DV18" s="5"/>
+      <c r="DW18" s="5"/>
+      <c r="DX18" s="5"/>
+      <c r="DY18" s="5"/>
+      <c r="DZ18" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:130">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AX19" s="5"/>
+      <c r="BM19" s="6"/>
+      <c r="CB19" s="5"/>
+      <c r="CS19" s="5"/>
+      <c r="DI19" s="5"/>
+      <c r="DZ19" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:130">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AX20" s="5"/>
+      <c r="BM20" s="6"/>
+      <c r="CB20" s="5"/>
+      <c r="CS20" s="5"/>
+      <c r="DI20" s="5"/>
+      <c r="DZ20" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:130">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AX21" s="5"/>
+      <c r="BM21" s="6"/>
+      <c r="CB21" s="5"/>
+      <c r="CS21" s="5"/>
+      <c r="DI21" s="5"/>
+      <c r="DZ21" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:130">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="5"/>
+      <c r="AG22" s="5"/>
+      <c r="AX22" s="5"/>
+      <c r="BM22" s="6"/>
+      <c r="CB22" s="5"/>
+      <c r="CS22" s="5"/>
+      <c r="DI22" s="5"/>
+      <c r="DZ22" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:130">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="5"/>
+      <c r="AG23" s="5"/>
+      <c r="AX23" s="5"/>
+      <c r="BM23" s="6"/>
+      <c r="CB23" s="5"/>
+      <c r="CS23" s="5"/>
+      <c r="DI23" s="5"/>
+      <c r="DZ23" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:130">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="AG24" s="5"/>
+      <c r="AX24" s="5"/>
+      <c r="BM24" s="6"/>
+      <c r="CB24" s="5"/>
+      <c r="CS24" s="5"/>
+      <c r="DI24" s="5"/>
+      <c r="DZ24" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:130">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="5"/>
+      <c r="AG25" s="5"/>
+      <c r="AX25" s="5"/>
+      <c r="BM25" s="6"/>
+      <c r="CB25" s="5"/>
+      <c r="CS25" s="5"/>
+      <c r="DI25" s="5"/>
+      <c r="DZ25" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:130">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="5"/>
+      <c r="AG26" s="5"/>
+      <c r="AX26" s="5"/>
+      <c r="BM26" s="6"/>
+      <c r="CB26" s="5"/>
+      <c r="CS26" s="5"/>
+      <c r="DI26" s="5"/>
+      <c r="DZ26" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:130">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AX27" s="5"/>
+      <c r="BM27" s="6"/>
+      <c r="CB27" s="5"/>
+      <c r="CS27" s="5"/>
+      <c r="DI27" s="5"/>
+      <c r="DZ27" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:130">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="5"/>
+      <c r="AG28" s="5"/>
+      <c r="AX28" s="5"/>
+      <c r="BM28" s="6"/>
+      <c r="CB28" s="5"/>
+      <c r="CS28" s="5"/>
+      <c r="DI28" s="5"/>
+      <c r="DZ28" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:130">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="5"/>
+      <c r="AG29" s="5"/>
+      <c r="AX29" s="5"/>
+      <c r="BM29" s="6"/>
+      <c r="CB29" s="5"/>
+      <c r="CS29" s="5"/>
+      <c r="DI29" s="5"/>
+      <c r="DZ29" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:130">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="Q30" s="5"/>
+      <c r="AG30" s="5"/>
+      <c r="AX30" s="5"/>
+      <c r="BM30" s="6"/>
+      <c r="CB30" s="5"/>
+      <c r="CS30" s="5"/>
+      <c r="DI30" s="5"/>
+      <c r="DZ30" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:130">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="Q31" s="5"/>
+      <c r="AG31" s="5"/>
+      <c r="AX31" s="5"/>
+      <c r="BM31" s="6"/>
+      <c r="CB31" s="5"/>
+      <c r="CS31" s="5"/>
+      <c r="DI31" s="5"/>
+      <c r="DZ31" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:130">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q32" s="5"/>
+      <c r="AG32" s="5"/>
+      <c r="AX32" s="5"/>
+      <c r="BM32" s="6"/>
+      <c r="CB32" s="5"/>
+      <c r="CS32" s="5"/>
+      <c r="DI32" s="5"/>
+      <c r="DZ32" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:130">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="Q33" s="5"/>
+      <c r="AG33" s="5"/>
+      <c r="AX33" s="5"/>
+      <c r="BM33" s="6"/>
+      <c r="CB33" s="5"/>
+      <c r="CS33" s="5"/>
+      <c r="DI33" s="5"/>
+      <c r="DZ33" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:130">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="6"/>
+      <c r="AL34" s="6"/>
+      <c r="AM34" s="6"/>
+      <c r="AN34" s="6"/>
+      <c r="AO34" s="6"/>
+      <c r="AP34" s="6"/>
+      <c r="AQ34" s="6"/>
+      <c r="AR34" s="6"/>
+      <c r="AS34" s="6"/>
+      <c r="AT34" s="6"/>
+      <c r="AU34" s="6"/>
+      <c r="AV34" s="6"/>
+      <c r="AW34" s="6"/>
+      <c r="AX34" s="6"/>
+      <c r="AY34" s="6"/>
+      <c r="AZ34" s="6"/>
+      <c r="BA34" s="6"/>
+      <c r="BB34" s="6"/>
+      <c r="BC34" s="6"/>
+      <c r="BD34" s="6"/>
+      <c r="BE34" s="6"/>
+      <c r="BF34" s="6"/>
+      <c r="BG34" s="6"/>
+      <c r="BH34" s="6"/>
+      <c r="BI34" s="6"/>
+      <c r="BJ34" s="6"/>
+      <c r="BK34" s="6"/>
+      <c r="BL34" s="6"/>
+      <c r="BM34" s="6"/>
+      <c r="BN34" s="6"/>
+      <c r="BO34" s="6"/>
+      <c r="BP34" s="6"/>
+      <c r="BQ34" s="6"/>
+      <c r="BR34" s="6"/>
+      <c r="BS34" s="6"/>
+      <c r="BT34" s="6"/>
+      <c r="BU34" s="6"/>
+      <c r="BV34" s="6"/>
+      <c r="BW34" s="6"/>
+      <c r="BX34" s="6"/>
+      <c r="BY34" s="6"/>
+      <c r="BZ34" s="6"/>
+      <c r="CA34" s="6"/>
+      <c r="CB34" s="6"/>
+      <c r="CC34" s="6"/>
+      <c r="CD34" s="6"/>
+      <c r="CE34" s="6"/>
+      <c r="CF34" s="6"/>
+      <c r="CG34" s="6"/>
+      <c r="CH34" s="6"/>
+      <c r="CI34" s="6"/>
+      <c r="CJ34" s="6"/>
+      <c r="CK34" s="6"/>
+      <c r="CL34" s="6"/>
+      <c r="CM34" s="6"/>
+      <c r="CN34" s="6"/>
+      <c r="CO34" s="6"/>
+      <c r="CP34" s="6"/>
+      <c r="CQ34" s="6"/>
+      <c r="CR34" s="6"/>
+      <c r="CS34" s="6"/>
+      <c r="CT34" s="6"/>
+      <c r="CU34" s="6"/>
+      <c r="CV34" s="6"/>
+      <c r="CW34" s="6"/>
+      <c r="CX34" s="6"/>
+      <c r="CY34" s="6"/>
+      <c r="CZ34" s="6"/>
+      <c r="DA34" s="6"/>
+      <c r="DB34" s="6"/>
+      <c r="DC34" s="6"/>
+      <c r="DD34" s="6"/>
+      <c r="DE34" s="6"/>
+      <c r="DF34" s="6"/>
+      <c r="DG34" s="6"/>
+      <c r="DH34" s="6"/>
+      <c r="DI34" s="6"/>
+      <c r="DJ34" s="6"/>
+      <c r="DK34" s="6"/>
+      <c r="DL34" s="6"/>
+      <c r="DM34" s="6"/>
+      <c r="DN34" s="6"/>
+      <c r="DO34" s="6"/>
+      <c r="DP34" s="6"/>
+      <c r="DQ34" s="6"/>
+      <c r="DR34" s="6"/>
+      <c r="DS34" s="6"/>
+      <c r="DT34" s="6"/>
+      <c r="DU34" s="6"/>
+      <c r="DV34" s="6"/>
+      <c r="DW34" s="6"/>
+      <c r="DX34" s="6"/>
+      <c r="DY34" s="6"/>
+      <c r="DZ34" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:130">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="Q35" s="5"/>
+      <c r="AG35" s="5"/>
+      <c r="AX35" s="5"/>
+      <c r="BM35" s="6"/>
+      <c r="CB35" s="5"/>
+      <c r="CS35" s="5"/>
+      <c r="DI35" s="5"/>
+      <c r="DZ35" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:130">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="Q36" s="5"/>
+      <c r="AG36" s="5"/>
+      <c r="AX36" s="5"/>
+      <c r="BM36" s="6"/>
+      <c r="CB36" s="5"/>
+      <c r="CS36" s="5"/>
+      <c r="DI36" s="5"/>
+      <c r="DZ36" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:130">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q37" s="5"/>
+      <c r="AG37" s="5"/>
+      <c r="AX37" s="5"/>
+      <c r="BM37" s="6"/>
+      <c r="CB37" s="5"/>
+      <c r="CS37" s="5"/>
+      <c r="DI37" s="5"/>
+      <c r="DZ37" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:130">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="Q38" s="5"/>
+      <c r="AG38" s="5"/>
+      <c r="AX38" s="5"/>
+      <c r="BM38" s="6"/>
+      <c r="CB38" s="5"/>
+      <c r="CS38" s="5"/>
+      <c r="DI38" s="5"/>
+      <c r="DZ38" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:130">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="Q39" s="5"/>
+      <c r="AG39" s="5"/>
+      <c r="AX39" s="5"/>
+      <c r="BM39" s="6"/>
+      <c r="CB39" s="5"/>
+      <c r="CS39" s="5"/>
+      <c r="DI39" s="5"/>
+      <c r="DZ39" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:130">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q40" s="5"/>
+      <c r="AG40" s="5"/>
+      <c r="AX40" s="5"/>
+      <c r="BM40" s="6"/>
+      <c r="CB40" s="5"/>
+      <c r="CS40" s="5"/>
+      <c r="DI40" s="5"/>
+      <c r="DZ40" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:130">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="Q41" s="5"/>
+      <c r="AG41" s="5"/>
+      <c r="AX41" s="5"/>
+      <c r="BM41" s="6"/>
+      <c r="CB41" s="5"/>
+      <c r="CS41" s="5"/>
+      <c r="DI41" s="5"/>
+      <c r="DZ41" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:130">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q42" s="5"/>
+      <c r="AG42" s="5"/>
+      <c r="AX42" s="5"/>
+      <c r="BM42" s="6"/>
+      <c r="CB42" s="5"/>
+      <c r="CS42" s="5"/>
+      <c r="DI42" s="5"/>
+      <c r="DZ42" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:130">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="Q43" s="5"/>
+      <c r="AG43" s="5"/>
+      <c r="AX43" s="5"/>
+      <c r="BM43" s="6"/>
+      <c r="CB43" s="5"/>
+      <c r="CS43" s="5"/>
+      <c r="DI43" s="5"/>
+      <c r="DZ43" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:130">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q44" s="5"/>
+      <c r="AG44" s="5"/>
+      <c r="AX44" s="5"/>
+      <c r="BM44" s="6"/>
+      <c r="CB44" s="5"/>
+      <c r="CS44" s="5"/>
+      <c r="DI44" s="5"/>
+      <c r="DZ44" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:130">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="Q45" s="5"/>
+      <c r="AG45" s="5"/>
+      <c r="AX45" s="5"/>
+      <c r="BM45" s="6"/>
+      <c r="CB45" s="5"/>
+      <c r="CS45" s="5"/>
+      <c r="DI45" s="5"/>
+      <c r="DZ45" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:130">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q46" s="5"/>
+      <c r="AG46" s="5"/>
+      <c r="AX46" s="5"/>
+      <c r="BM46" s="6"/>
+      <c r="CB46" s="5"/>
+      <c r="CS46" s="5"/>
+      <c r="DI46" s="5"/>
+      <c r="DZ46" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:130">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="Q47" s="5"/>
+      <c r="AG47" s="5"/>
+      <c r="AX47" s="5"/>
+      <c r="BM47" s="6"/>
+      <c r="CB47" s="5"/>
+      <c r="CS47" s="5"/>
+      <c r="DI47" s="5"/>
+      <c r="DZ47" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:130">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="5"/>
+      <c r="AG48" s="5"/>
+      <c r="AX48" s="5"/>
+      <c r="BM48" s="6"/>
+      <c r="CB48" s="5"/>
+      <c r="CS48" s="5"/>
+      <c r="DI48" s="5"/>
+      <c r="DZ48" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:130">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="Q49" s="5"/>
+      <c r="AG49" s="5"/>
+      <c r="AX49" s="5"/>
+      <c r="BM49" s="6"/>
+      <c r="CB49" s="5"/>
+      <c r="CS49" s="5"/>
+      <c r="DI49" s="5"/>
+      <c r="DZ49" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:130">
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
+      <c r="AC50" s="5"/>
+      <c r="AD50" s="5"/>
+      <c r="AE50" s="5"/>
+      <c r="AF50" s="5"/>
+      <c r="AG50" s="5"/>
+      <c r="AH50" s="5"/>
+      <c r="AI50" s="5"/>
+      <c r="AJ50" s="5"/>
+      <c r="AK50" s="5"/>
+      <c r="AL50" s="5"/>
+      <c r="AM50" s="5"/>
+      <c r="AN50" s="5"/>
+      <c r="AO50" s="5"/>
+      <c r="AP50" s="5"/>
+      <c r="AQ50" s="5"/>
+      <c r="AR50" s="5"/>
+      <c r="AS50" s="5"/>
+      <c r="AT50" s="5"/>
+      <c r="AU50" s="5"/>
+      <c r="AV50" s="5"/>
+      <c r="AW50" s="5"/>
+      <c r="AX50" s="5"/>
+      <c r="AY50" s="5"/>
+      <c r="AZ50" s="5"/>
+      <c r="BA50" s="5"/>
+      <c r="BB50" s="5"/>
+      <c r="BC50" s="5"/>
+      <c r="BD50" s="5"/>
+      <c r="BE50" s="5"/>
+      <c r="BF50" s="5"/>
+      <c r="BG50" s="5"/>
+      <c r="BH50" s="5"/>
+      <c r="BI50" s="5"/>
+      <c r="BJ50" s="5"/>
+      <c r="BK50" s="5"/>
+      <c r="BL50" s="5"/>
+      <c r="BM50" s="6"/>
+      <c r="BN50" s="5"/>
+      <c r="BO50" s="5"/>
+      <c r="BP50" s="5"/>
+      <c r="BQ50" s="5"/>
+      <c r="BR50" s="5"/>
+      <c r="BS50" s="5"/>
+      <c r="BT50" s="5"/>
+      <c r="BU50" s="5"/>
+      <c r="BV50" s="5"/>
+      <c r="BW50" s="5"/>
+      <c r="BX50" s="5"/>
+      <c r="BY50" s="5"/>
+      <c r="BZ50" s="5"/>
+      <c r="CA50" s="5"/>
+      <c r="CB50" s="5"/>
+      <c r="CC50" s="5"/>
+      <c r="CD50" s="5"/>
+      <c r="CE50" s="5"/>
+      <c r="CF50" s="5"/>
+      <c r="CG50" s="5"/>
+      <c r="CH50" s="5"/>
+      <c r="CI50" s="5"/>
+      <c r="CJ50" s="5"/>
+      <c r="CK50" s="5"/>
+      <c r="CL50" s="5"/>
+      <c r="CM50" s="5"/>
+      <c r="CN50" s="5"/>
+      <c r="CO50" s="5"/>
+      <c r="CP50" s="5"/>
+      <c r="CQ50" s="5"/>
+      <c r="CR50" s="5"/>
+      <c r="CS50" s="5"/>
+      <c r="CT50" s="5"/>
+      <c r="CU50" s="5"/>
+      <c r="CV50" s="5"/>
+      <c r="CW50" s="5"/>
+      <c r="CX50" s="5"/>
+      <c r="CY50" s="5"/>
+      <c r="CZ50" s="5"/>
+      <c r="DA50" s="5"/>
+      <c r="DB50" s="5"/>
+      <c r="DC50" s="5"/>
+      <c r="DD50" s="5"/>
+      <c r="DE50" s="5"/>
+      <c r="DF50" s="5"/>
+      <c r="DG50" s="5"/>
+      <c r="DH50" s="5"/>
+      <c r="DI50" s="5"/>
+      <c r="DJ50" s="5"/>
+      <c r="DK50" s="5"/>
+      <c r="DL50" s="5"/>
+      <c r="DM50" s="5"/>
+      <c r="DN50" s="5"/>
+      <c r="DO50" s="5"/>
+      <c r="DP50" s="5"/>
+      <c r="DQ50" s="5"/>
+      <c r="DR50" s="5"/>
+      <c r="DS50" s="5"/>
+      <c r="DT50" s="5"/>
+      <c r="DU50" s="5"/>
+      <c r="DV50" s="5"/>
+      <c r="DW50" s="5"/>
+      <c r="DX50" s="5"/>
+      <c r="DY50" s="5"/>
+      <c r="DZ50" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:130">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="Q51" s="5"/>
+      <c r="AG51" s="5"/>
+      <c r="AX51" s="5"/>
+      <c r="BM51" s="6"/>
+      <c r="CB51" s="5"/>
+      <c r="CS51" s="5"/>
+      <c r="DI51" s="5"/>
+      <c r="DZ51" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:130">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q52" s="5"/>
+      <c r="AG52" s="5"/>
+      <c r="AX52" s="5"/>
+      <c r="BM52" s="6"/>
+      <c r="CB52" s="5"/>
+      <c r="CS52" s="5"/>
+      <c r="DI52" s="5"/>
+      <c r="DZ52" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:130">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="Q53" s="5"/>
+      <c r="AG53" s="5"/>
+      <c r="AX53" s="5"/>
+      <c r="BM53" s="6"/>
+      <c r="CB53" s="5"/>
+      <c r="CS53" s="5"/>
+      <c r="DI53" s="5"/>
+      <c r="DZ53" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:130">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="Q54" s="5"/>
+      <c r="AG54" s="5"/>
+      <c r="AX54" s="5"/>
+      <c r="BM54" s="6"/>
+      <c r="CB54" s="5"/>
+      <c r="CS54" s="5"/>
+      <c r="DI54" s="5"/>
+      <c r="DZ54" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:130">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="Q55" s="5"/>
+      <c r="AG55" s="5"/>
+      <c r="AX55" s="5"/>
+      <c r="BM55" s="6"/>
+      <c r="CB55" s="5"/>
+      <c r="CS55" s="5"/>
+      <c r="DI55" s="5"/>
+      <c r="DZ55" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:130">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="Q56" s="5"/>
+      <c r="AG56" s="5"/>
+      <c r="AX56" s="5"/>
+      <c r="BM56" s="6"/>
+      <c r="CB56" s="5"/>
+      <c r="CS56" s="5"/>
+      <c r="DI56" s="5"/>
+      <c r="DZ56" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:130">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="Q57" s="5"/>
+      <c r="AG57" s="5"/>
+      <c r="AX57" s="5"/>
+      <c r="BM57" s="6"/>
+      <c r="CB57" s="5"/>
+      <c r="CS57" s="5"/>
+      <c r="DI57" s="5"/>
+      <c r="DZ57" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:130">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="Q58" s="5"/>
+      <c r="AG58" s="5"/>
+      <c r="AX58" s="5"/>
+      <c r="BM58" s="6"/>
+      <c r="CB58" s="5"/>
+      <c r="CS58" s="5"/>
+      <c r="DI58" s="5"/>
+      <c r="DZ58" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:130">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="Q59" s="5"/>
+      <c r="AG59" s="5"/>
+      <c r="AX59" s="5"/>
+      <c r="BM59" s="6"/>
+      <c r="CB59" s="5"/>
+      <c r="CS59" s="5"/>
+      <c r="DI59" s="5"/>
+      <c r="DZ59" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:130">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="Q60" s="5"/>
+      <c r="AG60" s="5"/>
+      <c r="AX60" s="5"/>
+      <c r="BM60" s="6"/>
+      <c r="CB60" s="5"/>
+      <c r="CS60" s="5"/>
+      <c r="DI60" s="5"/>
+      <c r="DZ60" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:130">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="Q61" s="5"/>
+      <c r="AG61" s="5"/>
+      <c r="AX61" s="5"/>
+      <c r="BM61" s="6"/>
+      <c r="CB61" s="5"/>
+      <c r="CS61" s="5"/>
+      <c r="DI61" s="5"/>
+      <c r="DZ61" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:130">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="Q62" s="5"/>
+      <c r="AG62" s="5"/>
+      <c r="AX62" s="5"/>
+      <c r="BM62" s="6"/>
+      <c r="CB62" s="5"/>
+      <c r="CS62" s="5"/>
+      <c r="DI62" s="5"/>
+      <c r="DZ62" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:130">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="Q63" s="5"/>
+      <c r="AG63" s="5"/>
+      <c r="AX63" s="5"/>
+      <c r="BM63" s="6"/>
+      <c r="CB63" s="5"/>
+      <c r="CS63" s="5"/>
+      <c r="DI63" s="5"/>
+      <c r="DZ63" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:130">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="Q64" s="5"/>
+      <c r="AG64" s="5"/>
+      <c r="AX64" s="5"/>
+      <c r="BM64" s="6"/>
+      <c r="CB64" s="5"/>
+      <c r="CS64" s="5"/>
+      <c r="DI64" s="5"/>
+      <c r="DZ64" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:130">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="Q65" s="5"/>
+      <c r="AG65" s="5"/>
+      <c r="AX65" s="5"/>
+      <c r="BM65" s="6"/>
+      <c r="CB65" s="5"/>
+      <c r="CS65" s="5"/>
+      <c r="DI65" s="5"/>
+      <c r="DZ65" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:130">
+      <c r="B66" s="1">
+        <v>0</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2">
+        <v>3</v>
+      </c>
+      <c r="F66" s="2">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2">
+        <v>5</v>
+      </c>
+      <c r="H66" s="2">
+        <v>6</v>
+      </c>
+      <c r="I66" s="2">
+        <v>7</v>
+      </c>
+      <c r="J66" s="2">
+        <v>8</v>
+      </c>
+      <c r="K66" s="2">
+        <v>9</v>
+      </c>
+      <c r="L66" s="2">
+        <v>10</v>
+      </c>
+      <c r="M66" s="2">
+        <v>11</v>
+      </c>
+      <c r="N66" s="2">
+        <v>12</v>
+      </c>
+      <c r="O66" s="2">
+        <v>13</v>
+      </c>
+      <c r="P66" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>15</v>
+      </c>
+      <c r="R66" s="2">
+        <v>16</v>
+      </c>
+      <c r="S66" s="2">
+        <v>17</v>
+      </c>
+      <c r="T66" s="2">
+        <v>18</v>
+      </c>
+      <c r="U66" s="2">
+        <v>19</v>
+      </c>
+      <c r="V66" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y66" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z66" s="2">
+        <v>24</v>
+      </c>
+      <c r="AA66" s="2">
+        <v>25</v>
+      </c>
+      <c r="AB66" s="2">
+        <v>26</v>
+      </c>
+      <c r="AC66" s="2">
+        <v>27</v>
+      </c>
+      <c r="AD66" s="2">
+        <v>28</v>
+      </c>
+      <c r="AE66" s="2">
+        <v>29</v>
+      </c>
+      <c r="AF66" s="2">
+        <v>30</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>31</v>
+      </c>
+      <c r="AH66" s="2">
+        <v>32</v>
+      </c>
+      <c r="AI66" s="2">
+        <v>33</v>
+      </c>
+      <c r="AJ66" s="2">
+        <v>34</v>
+      </c>
+      <c r="AK66" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL66" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM66" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN66" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO66" s="2">
+        <v>39</v>
+      </c>
+      <c r="AP66" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ66" s="2">
+        <v>41</v>
+      </c>
+      <c r="AR66" s="2">
+        <v>42</v>
+      </c>
+      <c r="AS66" s="2">
+        <v>43</v>
+      </c>
+      <c r="AT66" s="2">
+        <v>44</v>
+      </c>
+      <c r="AU66" s="2">
+        <v>45</v>
+      </c>
+      <c r="AV66" s="2">
+        <v>46</v>
+      </c>
+      <c r="AW66" s="2">
+        <v>47</v>
+      </c>
+      <c r="AX66" s="3">
+        <v>48</v>
+      </c>
+      <c r="AY66" s="2">
+        <v>49</v>
+      </c>
+      <c r="AZ66" s="2">
+        <v>50</v>
+      </c>
+      <c r="BA66" s="2">
+        <v>51</v>
+      </c>
+      <c r="BB66" s="2">
+        <v>52</v>
+      </c>
+      <c r="BC66" s="2">
+        <v>53</v>
+      </c>
+      <c r="BD66" s="2">
+        <v>54</v>
+      </c>
+      <c r="BE66" s="2">
+        <v>55</v>
+      </c>
+      <c r="BF66" s="2">
+        <v>56</v>
+      </c>
+      <c r="BG66" s="2">
+        <v>57</v>
+      </c>
+      <c r="BH66" s="2">
+        <v>58</v>
+      </c>
+      <c r="BI66" s="2">
+        <v>59</v>
+      </c>
+      <c r="BJ66" s="2">
+        <v>60</v>
+      </c>
+      <c r="BK66" s="2">
+        <v>61</v>
+      </c>
+      <c r="BL66" s="2">
+        <v>62</v>
+      </c>
+      <c r="BM66" s="3">
+        <v>63</v>
+      </c>
+      <c r="BN66" s="2">
+        <v>64</v>
+      </c>
+      <c r="BO66" s="2">
+        <v>65</v>
+      </c>
+      <c r="BP66" s="2">
+        <v>66</v>
+      </c>
+      <c r="BQ66" s="2">
+        <v>67</v>
+      </c>
+      <c r="BR66" s="2">
+        <v>68</v>
+      </c>
+      <c r="BS66" s="2">
+        <v>69</v>
+      </c>
+      <c r="BT66" s="2">
+        <v>70</v>
+      </c>
+      <c r="BU66" s="2">
+        <v>71</v>
+      </c>
+      <c r="BV66" s="2">
+        <v>72</v>
+      </c>
+      <c r="BW66" s="2">
+        <v>73</v>
+      </c>
+      <c r="BX66" s="2">
+        <v>74</v>
+      </c>
+      <c r="BY66" s="2">
+        <v>75</v>
+      </c>
+      <c r="BZ66" s="2">
+        <v>76</v>
+      </c>
+      <c r="CA66" s="2">
+        <v>77</v>
+      </c>
+      <c r="CB66" s="3">
+        <v>78</v>
+      </c>
+      <c r="CC66" s="2">
+        <v>79</v>
+      </c>
+      <c r="CD66" s="2">
+        <v>80</v>
+      </c>
+      <c r="CE66" s="2">
+        <v>81</v>
+      </c>
+      <c r="CF66" s="2">
+        <v>82</v>
+      </c>
+      <c r="CG66" s="2">
+        <v>83</v>
+      </c>
+      <c r="CH66" s="2">
+        <v>84</v>
+      </c>
+      <c r="CI66" s="2">
+        <v>85</v>
+      </c>
+      <c r="CJ66" s="2">
+        <v>86</v>
+      </c>
+      <c r="CK66" s="2">
+        <v>87</v>
+      </c>
+      <c r="CL66" s="2">
+        <v>88</v>
+      </c>
+      <c r="CM66" s="2">
+        <v>89</v>
+      </c>
+      <c r="CN66" s="2">
+        <v>90</v>
+      </c>
+      <c r="CO66" s="2">
+        <v>91</v>
+      </c>
+      <c r="CP66" s="2">
+        <v>92</v>
+      </c>
+      <c r="CQ66" s="2">
+        <v>93</v>
+      </c>
+      <c r="CR66" s="2">
+        <v>94</v>
+      </c>
+      <c r="CS66" s="3">
+        <v>95</v>
+      </c>
+      <c r="CT66" s="2">
+        <v>96</v>
+      </c>
+      <c r="CU66" s="2">
+        <v>97</v>
+      </c>
+      <c r="CV66" s="2">
+        <v>98</v>
+      </c>
+      <c r="CW66" s="2">
+        <v>99</v>
+      </c>
+      <c r="CX66" s="2">
+        <v>100</v>
+      </c>
+      <c r="CY66" s="2">
+        <v>101</v>
+      </c>
+      <c r="CZ66" s="2">
+        <v>102</v>
+      </c>
+      <c r="DA66" s="2">
+        <v>103</v>
+      </c>
+      <c r="DB66" s="2">
+        <v>104</v>
+      </c>
+      <c r="DC66" s="2">
+        <v>105</v>
+      </c>
+      <c r="DD66" s="2">
+        <v>106</v>
+      </c>
+      <c r="DE66" s="2">
+        <v>107</v>
+      </c>
+      <c r="DF66" s="2">
+        <v>108</v>
+      </c>
+      <c r="DG66" s="2">
+        <v>109</v>
+      </c>
+      <c r="DH66" s="2">
+        <v>110</v>
+      </c>
+      <c r="DI66" s="3">
+        <v>111</v>
+      </c>
+      <c r="DJ66" s="2">
+        <v>112</v>
+      </c>
+      <c r="DK66" s="2">
+        <v>113</v>
+      </c>
+      <c r="DL66" s="2">
+        <v>114</v>
+      </c>
+      <c r="DM66" s="2">
+        <v>115</v>
+      </c>
+      <c r="DN66" s="2">
+        <v>116</v>
+      </c>
+      <c r="DO66" s="2">
+        <v>117</v>
+      </c>
+      <c r="DP66" s="2">
+        <v>118</v>
+      </c>
+      <c r="DQ66" s="2">
+        <v>119</v>
+      </c>
+      <c r="DR66" s="2">
+        <v>120</v>
+      </c>
+      <c r="DS66" s="2">
+        <v>121</v>
+      </c>
+      <c r="DT66" s="2">
+        <v>122</v>
+      </c>
+      <c r="DU66" s="2">
+        <v>123</v>
+      </c>
+      <c r="DV66" s="2">
+        <v>124</v>
+      </c>
+      <c r="DW66" s="2">
+        <v>125</v>
+      </c>
+      <c r="DX66" s="2">
+        <v>126</v>
+      </c>
+      <c r="DY66" s="2">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B0B573-2327-47F2-8B26-01950D0ED9D2}">
+  <dimension ref="A1:DZ66"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="3.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:130">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2">
+        <v>18</v>
+      </c>
+      <c r="U1" s="2">
+        <v>19</v>
+      </c>
+      <c r="V1" s="2">
+        <v>20</v>
+      </c>
+      <c r="W1" s="2">
+        <v>21</v>
+      </c>
+      <c r="X1" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="2">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="2">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="2">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="2">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="2">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="2">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="2">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="2">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="2">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="2">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="2">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="2">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="2">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="2">
+        <v>52</v>
+      </c>
+      <c r="BC1" s="2">
+        <v>53</v>
+      </c>
+      <c r="BD1" s="2">
+        <v>54</v>
+      </c>
+      <c r="BE1" s="2">
+        <v>55</v>
+      </c>
+      <c r="BF1" s="2">
+        <v>56</v>
+      </c>
+      <c r="BG1" s="2">
+        <v>57</v>
+      </c>
+      <c r="BH1" s="2">
+        <v>58</v>
+      </c>
+      <c r="BI1" s="2">
+        <v>59</v>
+      </c>
+      <c r="BJ1" s="2">
+        <v>60</v>
+      </c>
+      <c r="BK1" s="2">
+        <v>61</v>
+      </c>
+      <c r="BL1" s="2">
+        <v>62</v>
+      </c>
+      <c r="BM1" s="3">
+        <v>63</v>
+      </c>
+      <c r="BN1" s="2">
+        <v>64</v>
+      </c>
+      <c r="BO1" s="2">
+        <v>65</v>
+      </c>
+      <c r="BP1" s="2">
+        <v>66</v>
+      </c>
+      <c r="BQ1" s="2">
+        <v>67</v>
+      </c>
+      <c r="BR1" s="2">
+        <v>68</v>
+      </c>
+      <c r="BS1" s="2">
+        <v>69</v>
+      </c>
+      <c r="BT1" s="2">
+        <v>70</v>
+      </c>
+      <c r="BU1" s="2">
+        <v>71</v>
+      </c>
+      <c r="BV1" s="2">
+        <v>72</v>
+      </c>
+      <c r="BW1" s="2">
+        <v>73</v>
+      </c>
+      <c r="BX1" s="2">
+        <v>74</v>
+      </c>
+      <c r="BY1" s="2">
+        <v>75</v>
+      </c>
+      <c r="BZ1" s="2">
+        <v>76</v>
+      </c>
+      <c r="CA1" s="2">
+        <v>77</v>
+      </c>
+      <c r="CB1" s="3">
+        <v>78</v>
+      </c>
+      <c r="CC1" s="2">
+        <v>79</v>
+      </c>
+      <c r="CD1" s="2">
+        <v>80</v>
+      </c>
+      <c r="CE1" s="2">
+        <v>81</v>
+      </c>
+      <c r="CF1" s="2">
+        <v>82</v>
+      </c>
+      <c r="CG1" s="2">
+        <v>83</v>
+      </c>
+      <c r="CH1" s="2">
+        <v>84</v>
+      </c>
+      <c r="CI1" s="2">
+        <v>85</v>
+      </c>
+      <c r="CJ1" s="2">
+        <v>86</v>
+      </c>
+      <c r="CK1" s="2">
+        <v>87</v>
+      </c>
+      <c r="CL1" s="2">
+        <v>88</v>
+      </c>
+      <c r="CM1" s="2">
+        <v>89</v>
+      </c>
+      <c r="CN1" s="2">
+        <v>90</v>
+      </c>
+      <c r="CO1" s="2">
+        <v>91</v>
+      </c>
+      <c r="CP1" s="2">
+        <v>92</v>
+      </c>
+      <c r="CQ1" s="2">
+        <v>93</v>
+      </c>
+      <c r="CR1" s="2">
+        <v>94</v>
+      </c>
+      <c r="CS1" s="3">
+        <v>95</v>
+      </c>
+      <c r="CT1" s="2">
+        <v>96</v>
+      </c>
+      <c r="CU1" s="2">
+        <v>97</v>
+      </c>
+      <c r="CV1" s="2">
+        <v>98</v>
+      </c>
+      <c r="CW1" s="2">
+        <v>99</v>
+      </c>
+      <c r="CX1" s="2">
+        <v>100</v>
+      </c>
+      <c r="CY1" s="2">
+        <v>101</v>
+      </c>
+      <c r="CZ1" s="2">
+        <v>102</v>
+      </c>
+      <c r="DA1" s="2">
+        <v>103</v>
+      </c>
+      <c r="DB1" s="2">
+        <v>104</v>
+      </c>
+      <c r="DC1" s="2">
+        <v>105</v>
+      </c>
+      <c r="DD1" s="2">
+        <v>106</v>
+      </c>
+      <c r="DE1" s="2">
+        <v>107</v>
+      </c>
+      <c r="DF1" s="2">
+        <v>108</v>
+      </c>
+      <c r="DG1" s="2">
+        <v>109</v>
+      </c>
+      <c r="DH1" s="2">
+        <v>110</v>
+      </c>
+      <c r="DI1" s="3">
+        <v>111</v>
+      </c>
+      <c r="DJ1" s="2">
+        <v>112</v>
+      </c>
+      <c r="DK1" s="2">
+        <v>113</v>
+      </c>
+      <c r="DL1" s="2">
+        <v>114</v>
+      </c>
+      <c r="DM1" s="2">
+        <v>115</v>
+      </c>
+      <c r="DN1" s="2">
+        <v>116</v>
+      </c>
+      <c r="DO1" s="2">
+        <v>117</v>
+      </c>
+      <c r="DP1" s="2">
+        <v>118</v>
+      </c>
+      <c r="DQ1" s="2">
+        <v>119</v>
+      </c>
+      <c r="DR1" s="2">
+        <v>120</v>
+      </c>
+      <c r="DS1" s="2">
+        <v>121</v>
+      </c>
+      <c r="DT1" s="2">
+        <v>122</v>
+      </c>
+      <c r="DU1" s="2">
+        <v>123</v>
+      </c>
+      <c r="DV1" s="2">
+        <v>124</v>
+      </c>
+      <c r="DW1" s="2">
+        <v>125</v>
+      </c>
+      <c r="DX1" s="2">
+        <v>126</v>
+      </c>
+      <c r="DY1" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:130">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="BM2" s="6"/>
+      <c r="CB2" s="5"/>
+      <c r="CS2" s="5"/>
+      <c r="DI2" s="5"/>
+      <c r="DZ2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:130">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="BM3" s="6"/>
+      <c r="CB3" s="5"/>
+      <c r="CS3" s="5"/>
+      <c r="DI3" s="5"/>
+      <c r="DZ3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:130">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="BM4" s="6"/>
+      <c r="CB4" s="5"/>
+      <c r="CS4" s="5"/>
+      <c r="DI4" s="5"/>
+      <c r="DZ4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:130">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="BM5" s="6"/>
+      <c r="CB5" s="5"/>
+      <c r="CS5" s="5"/>
+      <c r="DI5" s="5"/>
+      <c r="DZ5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:130">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AX6" s="5"/>
+      <c r="BM6" s="6"/>
+      <c r="CB6" s="5"/>
+      <c r="CS6" s="5"/>
+      <c r="DI6" s="5"/>
+      <c r="DZ6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:130">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AX7" s="5"/>
+      <c r="BM7" s="6"/>
+      <c r="CB7" s="5"/>
+      <c r="CS7" s="5"/>
+      <c r="DI7" s="5"/>
+      <c r="DZ7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:130">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AX8" s="5"/>
+      <c r="BM8" s="6"/>
+      <c r="CB8" s="5"/>
+      <c r="CS8" s="5"/>
+      <c r="DI8" s="5"/>
+      <c r="DZ8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:130">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AX9" s="5"/>
+      <c r="BM9" s="6"/>
+      <c r="CB9" s="5"/>
+      <c r="CS9" s="5"/>
+      <c r="DI9" s="5"/>
+      <c r="DZ9" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:130">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AX10" s="5"/>
+      <c r="BM10" s="6"/>
+      <c r="CB10" s="5"/>
+      <c r="CS10" s="5"/>
+      <c r="DI10" s="5"/>
+      <c r="DZ10" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:130">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AX11" s="5"/>
+      <c r="BM11" s="6"/>
+      <c r="CB11" s="5"/>
+      <c r="CS11" s="5"/>
+      <c r="DI11" s="5"/>
+      <c r="DZ11" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:130">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AX12" s="5"/>
+      <c r="BM12" s="6"/>
+      <c r="CB12" s="5"/>
+      <c r="CS12" s="5"/>
+      <c r="DI12" s="5"/>
+      <c r="DZ12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:130">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AX13" s="5"/>
+      <c r="BM13" s="6"/>
+      <c r="CB13" s="5"/>
+      <c r="CS13" s="5"/>
+      <c r="DI13" s="5"/>
+      <c r="DZ13" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:130">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AX14" s="5"/>
+      <c r="BM14" s="6"/>
+      <c r="CB14" s="5"/>
+      <c r="CS14" s="5"/>
+      <c r="DI14" s="5"/>
+      <c r="DZ14" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:130">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AX15" s="5"/>
+      <c r="BM15" s="6"/>
+      <c r="CB15" s="5"/>
+      <c r="CS15" s="5"/>
+      <c r="DI15" s="5"/>
+      <c r="DZ15" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:130">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AX16" s="5"/>
+      <c r="BM16" s="6"/>
+      <c r="CB16" s="5"/>
+      <c r="CS16" s="5"/>
+      <c r="DI16" s="5"/>
+      <c r="DZ16" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:130">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="AG17" s="5"/>
+      <c r="AX17" s="5"/>
+      <c r="BM17" s="6"/>
+      <c r="CB17" s="5"/>
+      <c r="CS17" s="5"/>
+      <c r="DI17" s="5"/>
+      <c r="DZ17" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:130">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="5"/>
+      <c r="AS18" s="5"/>
+      <c r="AT18" s="5"/>
+      <c r="AU18" s="5"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="5"/>
+      <c r="AY18" s="5"/>
+      <c r="AZ18" s="5"/>
+      <c r="BA18" s="5"/>
+      <c r="BB18" s="5"/>
+      <c r="BC18" s="5"/>
+      <c r="BD18" s="5"/>
+      <c r="BE18" s="5"/>
+      <c r="BF18" s="5"/>
+      <c r="BG18" s="5"/>
+      <c r="BH18" s="5"/>
+      <c r="BI18" s="5"/>
+      <c r="BJ18" s="5"/>
+      <c r="BK18" s="5"/>
+      <c r="BL18" s="5"/>
+      <c r="BM18" s="6"/>
+      <c r="BN18" s="5"/>
+      <c r="BO18" s="5"/>
+      <c r="BP18" s="5"/>
+      <c r="BQ18" s="5"/>
+      <c r="BR18" s="5"/>
+      <c r="BS18" s="5"/>
+      <c r="BT18" s="5"/>
+      <c r="BU18" s="5"/>
+      <c r="BV18" s="5"/>
+      <c r="BW18" s="5"/>
+      <c r="BX18" s="5"/>
+      <c r="BY18" s="5"/>
+      <c r="BZ18" s="5"/>
+      <c r="CA18" s="5"/>
+      <c r="CB18" s="5"/>
+      <c r="CC18" s="5"/>
+      <c r="CD18" s="5"/>
+      <c r="CE18" s="5"/>
+      <c r="CF18" s="5"/>
+      <c r="CG18" s="5"/>
+      <c r="CH18" s="5"/>
+      <c r="CI18" s="5"/>
+      <c r="CJ18" s="5"/>
+      <c r="CK18" s="5"/>
+      <c r="CL18" s="5"/>
+      <c r="CM18" s="5"/>
+      <c r="CN18" s="5"/>
+      <c r="CO18" s="5"/>
+      <c r="CP18" s="5"/>
+      <c r="CQ18" s="5"/>
+      <c r="CR18" s="5"/>
+      <c r="CS18" s="5"/>
+      <c r="CT18" s="5"/>
+      <c r="CU18" s="5"/>
+      <c r="CV18" s="5"/>
+      <c r="CW18" s="5"/>
+      <c r="CX18" s="5"/>
+      <c r="CY18" s="5"/>
+      <c r="CZ18" s="5"/>
+      <c r="DA18" s="5"/>
+      <c r="DB18" s="5"/>
+      <c r="DC18" s="5"/>
+      <c r="DD18" s="5"/>
+      <c r="DE18" s="5"/>
+      <c r="DF18" s="5"/>
+      <c r="DG18" s="5"/>
+      <c r="DH18" s="5"/>
+      <c r="DI18" s="5"/>
+      <c r="DJ18" s="5"/>
+      <c r="DK18" s="5"/>
+      <c r="DL18" s="5"/>
+      <c r="DM18" s="5"/>
+      <c r="DN18" s="5"/>
+      <c r="DO18" s="5"/>
+      <c r="DP18" s="5"/>
+      <c r="DQ18" s="5"/>
+      <c r="DR18" s="5"/>
+      <c r="DS18" s="5"/>
+      <c r="DT18" s="5"/>
+      <c r="DU18" s="5"/>
+      <c r="DV18" s="5"/>
+      <c r="DW18" s="5"/>
+      <c r="DX18" s="5"/>
+      <c r="DY18" s="5"/>
+      <c r="DZ18" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:130">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AX19" s="5"/>
+      <c r="BM19" s="6"/>
+      <c r="CB19" s="5"/>
+      <c r="CS19" s="5"/>
+      <c r="DI19" s="5"/>
+      <c r="DZ19" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:130">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AX20" s="5"/>
+      <c r="BM20" s="6"/>
+      <c r="CB20" s="5"/>
+      <c r="CS20" s="5"/>
+      <c r="DI20" s="5"/>
+      <c r="DZ20" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:130">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AX21" s="5"/>
+      <c r="BM21" s="6"/>
+      <c r="CB21" s="5"/>
+      <c r="CS21" s="5"/>
+      <c r="DI21" s="5"/>
+      <c r="DZ21" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:130">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="5"/>
+      <c r="AG22" s="5"/>
+      <c r="AX22" s="5"/>
+      <c r="BM22" s="6"/>
+      <c r="CB22" s="5"/>
+      <c r="CS22" s="5"/>
+      <c r="DI22" s="5"/>
+      <c r="DZ22" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:130">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="5"/>
+      <c r="AG23" s="5"/>
+      <c r="AX23" s="5"/>
+      <c r="BM23" s="6"/>
+      <c r="CB23" s="5"/>
+      <c r="CS23" s="5"/>
+      <c r="DI23" s="5"/>
+      <c r="DZ23" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:130">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="AG24" s="5"/>
+      <c r="AX24" s="5"/>
+      <c r="BM24" s="6"/>
+      <c r="CB24" s="5"/>
+      <c r="CS24" s="5"/>
+      <c r="DI24" s="5"/>
+      <c r="DZ24" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:130">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="5"/>
+      <c r="AG25" s="5"/>
+      <c r="AX25" s="5"/>
+      <c r="BM25" s="6"/>
+      <c r="CB25" s="5"/>
+      <c r="CS25" s="5"/>
+      <c r="DI25" s="5"/>
+      <c r="DZ25" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:130">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="5"/>
+      <c r="AG26" s="5"/>
+      <c r="AX26" s="5"/>
+      <c r="BM26" s="6"/>
+      <c r="CB26" s="5"/>
+      <c r="CS26" s="5"/>
+      <c r="DI26" s="5"/>
+      <c r="DZ26" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:130">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AX27" s="5"/>
+      <c r="BM27" s="6"/>
+      <c r="CB27" s="5"/>
+      <c r="CS27" s="5"/>
+      <c r="DI27" s="5"/>
+      <c r="DZ27" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:130">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="5"/>
+      <c r="AG28" s="5"/>
+      <c r="AX28" s="5"/>
+      <c r="BM28" s="6"/>
+      <c r="CB28" s="5"/>
+      <c r="CS28" s="5"/>
+      <c r="DI28" s="5"/>
+      <c r="DZ28" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:130">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="5"/>
+      <c r="AG29" s="5"/>
+      <c r="AX29" s="5"/>
+      <c r="BM29" s="6"/>
+      <c r="CB29" s="5"/>
+      <c r="CS29" s="5"/>
+      <c r="DI29" s="5"/>
+      <c r="DZ29" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:130">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="Q30" s="5"/>
+      <c r="AG30" s="5"/>
+      <c r="AX30" s="5"/>
+      <c r="BM30" s="6"/>
+      <c r="CB30" s="5"/>
+      <c r="CS30" s="5"/>
+      <c r="DI30" s="5"/>
+      <c r="DZ30" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:130">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="Q31" s="5"/>
+      <c r="AG31" s="5"/>
+      <c r="AX31" s="5"/>
+      <c r="BM31" s="6"/>
+      <c r="CB31" s="5"/>
+      <c r="CS31" s="5"/>
+      <c r="DI31" s="5"/>
+      <c r="DZ31" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:130">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q32" s="5"/>
+      <c r="AG32" s="5"/>
+      <c r="AX32" s="5"/>
+      <c r="BM32" s="6"/>
+      <c r="CB32" s="5"/>
+      <c r="CS32" s="5"/>
+      <c r="DI32" s="5"/>
+      <c r="DZ32" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:130">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="Q33" s="5"/>
+      <c r="AG33" s="5"/>
+      <c r="AX33" s="5"/>
+      <c r="BM33" s="6"/>
+      <c r="CB33" s="5"/>
+      <c r="CS33" s="5"/>
+      <c r="DI33" s="5"/>
+      <c r="DZ33" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:130">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="6"/>
+      <c r="AL34" s="6"/>
+      <c r="AM34" s="6"/>
+      <c r="AN34" s="6"/>
+      <c r="AO34" s="6"/>
+      <c r="AP34" s="6"/>
+      <c r="AQ34" s="6"/>
+      <c r="AR34" s="6"/>
+      <c r="AS34" s="6"/>
+      <c r="AT34" s="6"/>
+      <c r="AU34" s="6"/>
+      <c r="AV34" s="6"/>
+      <c r="AW34" s="6"/>
+      <c r="AX34" s="6"/>
+      <c r="AY34" s="6"/>
+      <c r="AZ34" s="6"/>
+      <c r="BA34" s="6"/>
+      <c r="BB34" s="6"/>
+      <c r="BC34" s="6"/>
+      <c r="BD34" s="6"/>
+      <c r="BE34" s="6"/>
+      <c r="BF34" s="6"/>
+      <c r="BG34" s="6"/>
+      <c r="BH34" s="6"/>
+      <c r="BI34" s="6"/>
+      <c r="BJ34" s="6"/>
+      <c r="BK34" s="6"/>
+      <c r="BL34" s="6"/>
+      <c r="BM34" s="6"/>
+      <c r="BN34" s="6"/>
+      <c r="BO34" s="6"/>
+      <c r="BP34" s="6"/>
+      <c r="BQ34" s="6"/>
+      <c r="BR34" s="6"/>
+      <c r="BS34" s="6"/>
+      <c r="BT34" s="6"/>
+      <c r="BU34" s="6"/>
+      <c r="BV34" s="6"/>
+      <c r="BW34" s="6"/>
+      <c r="BX34" s="6"/>
+      <c r="BY34" s="6"/>
+      <c r="BZ34" s="6"/>
+      <c r="CA34" s="6"/>
+      <c r="CB34" s="6"/>
+      <c r="CC34" s="6"/>
+      <c r="CD34" s="6"/>
+      <c r="CE34" s="6"/>
+      <c r="CF34" s="6"/>
+      <c r="CG34" s="6"/>
+      <c r="CH34" s="6"/>
+      <c r="CI34" s="6"/>
+      <c r="CJ34" s="6"/>
+      <c r="CK34" s="6"/>
+      <c r="CL34" s="6"/>
+      <c r="CM34" s="6"/>
+      <c r="CN34" s="6"/>
+      <c r="CO34" s="6"/>
+      <c r="CP34" s="6"/>
+      <c r="CQ34" s="6"/>
+      <c r="CR34" s="6"/>
+      <c r="CS34" s="6"/>
+      <c r="CT34" s="6"/>
+      <c r="CU34" s="6"/>
+      <c r="CV34" s="6"/>
+      <c r="CW34" s="6"/>
+      <c r="CX34" s="6"/>
+      <c r="CY34" s="6"/>
+      <c r="CZ34" s="6"/>
+      <c r="DA34" s="6"/>
+      <c r="DB34" s="6"/>
+      <c r="DC34" s="6"/>
+      <c r="DD34" s="6"/>
+      <c r="DE34" s="6"/>
+      <c r="DF34" s="6"/>
+      <c r="DG34" s="6"/>
+      <c r="DH34" s="6"/>
+      <c r="DI34" s="6"/>
+      <c r="DJ34" s="6"/>
+      <c r="DK34" s="6"/>
+      <c r="DL34" s="6"/>
+      <c r="DM34" s="6"/>
+      <c r="DN34" s="6"/>
+      <c r="DO34" s="6"/>
+      <c r="DP34" s="6"/>
+      <c r="DQ34" s="6"/>
+      <c r="DR34" s="6"/>
+      <c r="DS34" s="6"/>
+      <c r="DT34" s="6"/>
+      <c r="DU34" s="6"/>
+      <c r="DV34" s="6"/>
+      <c r="DW34" s="6"/>
+      <c r="DX34" s="6"/>
+      <c r="DY34" s="6"/>
+      <c r="DZ34" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:130">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="Q35" s="5"/>
+      <c r="AG35" s="5"/>
+      <c r="AX35" s="5"/>
+      <c r="BM35" s="6"/>
+      <c r="CB35" s="5"/>
+      <c r="CS35" s="5"/>
+      <c r="DI35" s="5"/>
+      <c r="DZ35" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:130">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="Q36" s="5"/>
+      <c r="AG36" s="5"/>
+      <c r="AX36" s="5"/>
+      <c r="BM36" s="6"/>
+      <c r="CB36" s="5"/>
+      <c r="CS36" s="5"/>
+      <c r="DI36" s="5"/>
+      <c r="DZ36" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:130">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q37" s="5"/>
+      <c r="AG37" s="5"/>
+      <c r="AX37" s="5"/>
+      <c r="BM37" s="6"/>
+      <c r="CB37" s="5"/>
+      <c r="CS37" s="5"/>
+      <c r="DI37" s="5"/>
+      <c r="DZ37" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:130">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="Q38" s="5"/>
+      <c r="AG38" s="5"/>
+      <c r="AX38" s="5"/>
+      <c r="BM38" s="6"/>
+      <c r="CB38" s="5"/>
+      <c r="CS38" s="5"/>
+      <c r="DI38" s="5"/>
+      <c r="DZ38" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:130">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="Q39" s="5"/>
+      <c r="AG39" s="5"/>
+      <c r="AX39" s="5"/>
+      <c r="BM39" s="6"/>
+      <c r="CB39" s="5"/>
+      <c r="CS39" s="5"/>
+      <c r="DI39" s="5"/>
+      <c r="DZ39" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:130">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q40" s="5"/>
+      <c r="AG40" s="5"/>
+      <c r="AX40" s="5"/>
+      <c r="BM40" s="6"/>
+      <c r="CB40" s="5"/>
+      <c r="CS40" s="5"/>
+      <c r="DI40" s="5"/>
+      <c r="DZ40" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:130">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="Q41" s="5"/>
+      <c r="AG41" s="5"/>
+      <c r="AX41" s="5"/>
+      <c r="BM41" s="6"/>
+      <c r="CB41" s="5"/>
+      <c r="CS41" s="5"/>
+      <c r="DI41" s="5"/>
+      <c r="DZ41" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:130">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q42" s="5"/>
+      <c r="AG42" s="5"/>
+      <c r="AX42" s="5"/>
+      <c r="BM42" s="6"/>
+      <c r="CB42" s="5"/>
+      <c r="CS42" s="5"/>
+      <c r="DI42" s="5"/>
+      <c r="DZ42" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:130">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="Q43" s="5"/>
+      <c r="AG43" s="5"/>
+      <c r="AX43" s="5"/>
+      <c r="BM43" s="6"/>
+      <c r="CB43" s="5"/>
+      <c r="CS43" s="5"/>
+      <c r="DI43" s="5"/>
+      <c r="DZ43" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:130">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q44" s="5"/>
+      <c r="AG44" s="5"/>
+      <c r="AX44" s="5"/>
+      <c r="BM44" s="6"/>
+      <c r="CB44" s="5"/>
+      <c r="CS44" s="5"/>
+      <c r="DI44" s="5"/>
+      <c r="DZ44" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:130">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="Q45" s="5"/>
+      <c r="AG45" s="5"/>
+      <c r="AX45" s="5"/>
+      <c r="BM45" s="6"/>
+      <c r="CB45" s="5"/>
+      <c r="CS45" s="5"/>
+      <c r="DI45" s="5"/>
+      <c r="DZ45" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:130">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q46" s="5"/>
+      <c r="AG46" s="5"/>
+      <c r="AX46" s="5"/>
+      <c r="BM46" s="6"/>
+      <c r="CB46" s="5"/>
+      <c r="CS46" s="5"/>
+      <c r="DI46" s="5"/>
+      <c r="DZ46" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:130">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="Q47" s="5"/>
+      <c r="AG47" s="5"/>
+      <c r="AX47" s="5"/>
+      <c r="BM47" s="6"/>
+      <c r="CB47" s="5"/>
+      <c r="CS47" s="5"/>
+      <c r="DI47" s="5"/>
+      <c r="DZ47" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:130">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="5"/>
+      <c r="AG48" s="5"/>
+      <c r="AX48" s="5"/>
+      <c r="BM48" s="6"/>
+      <c r="CB48" s="5"/>
+      <c r="CS48" s="5"/>
+      <c r="DI48" s="5"/>
+      <c r="DZ48" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:130">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="Q49" s="5"/>
+      <c r="AG49" s="5"/>
+      <c r="AX49" s="5"/>
+      <c r="BM49" s="6"/>
+      <c r="CB49" s="5"/>
+      <c r="CS49" s="5"/>
+      <c r="DI49" s="5"/>
+      <c r="DZ49" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:130">
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
+      <c r="AC50" s="5"/>
+      <c r="AD50" s="5"/>
+      <c r="AE50" s="5"/>
+      <c r="AF50" s="5"/>
+      <c r="AG50" s="5"/>
+      <c r="AH50" s="5"/>
+      <c r="AI50" s="5"/>
+      <c r="AJ50" s="5"/>
+      <c r="AK50" s="5"/>
+      <c r="AL50" s="5"/>
+      <c r="AM50" s="5"/>
+      <c r="AN50" s="5"/>
+      <c r="AO50" s="5"/>
+      <c r="AP50" s="5"/>
+      <c r="AQ50" s="5"/>
+      <c r="AR50" s="5"/>
+      <c r="AS50" s="5"/>
+      <c r="AT50" s="5"/>
+      <c r="AU50" s="5"/>
+      <c r="AV50" s="5"/>
+      <c r="AW50" s="5"/>
+      <c r="AX50" s="5"/>
+      <c r="AY50" s="5"/>
+      <c r="AZ50" s="5"/>
+      <c r="BA50" s="5"/>
+      <c r="BB50" s="5"/>
+      <c r="BC50" s="5"/>
+      <c r="BD50" s="5"/>
+      <c r="BE50" s="5"/>
+      <c r="BF50" s="5"/>
+      <c r="BG50" s="5"/>
+      <c r="BH50" s="5"/>
+      <c r="BI50" s="5"/>
+      <c r="BJ50" s="5"/>
+      <c r="BK50" s="5"/>
+      <c r="BL50" s="5"/>
+      <c r="BM50" s="6"/>
+      <c r="BN50" s="5"/>
+      <c r="BO50" s="5"/>
+      <c r="BP50" s="5"/>
+      <c r="BQ50" s="5"/>
+      <c r="BR50" s="5"/>
+      <c r="BS50" s="5"/>
+      <c r="BT50" s="5"/>
+      <c r="BU50" s="5"/>
+      <c r="BV50" s="5"/>
+      <c r="BW50" s="5"/>
+      <c r="BX50" s="5"/>
+      <c r="BY50" s="5"/>
+      <c r="BZ50" s="5"/>
+      <c r="CA50" s="5"/>
+      <c r="CB50" s="5"/>
+      <c r="CC50" s="5"/>
+      <c r="CD50" s="5"/>
+      <c r="CE50" s="5"/>
+      <c r="CF50" s="5"/>
+      <c r="CG50" s="5"/>
+      <c r="CH50" s="5"/>
+      <c r="CI50" s="5"/>
+      <c r="CJ50" s="5"/>
+      <c r="CK50" s="5"/>
+      <c r="CL50" s="5"/>
+      <c r="CM50" s="5"/>
+      <c r="CN50" s="5"/>
+      <c r="CO50" s="5"/>
+      <c r="CP50" s="5"/>
+      <c r="CQ50" s="5"/>
+      <c r="CR50" s="5"/>
+      <c r="CS50" s="5"/>
+      <c r="CT50" s="5"/>
+      <c r="CU50" s="5"/>
+      <c r="CV50" s="5"/>
+      <c r="CW50" s="5"/>
+      <c r="CX50" s="5"/>
+      <c r="CY50" s="5"/>
+      <c r="CZ50" s="5"/>
+      <c r="DA50" s="5"/>
+      <c r="DB50" s="5"/>
+      <c r="DC50" s="5"/>
+      <c r="DD50" s="5"/>
+      <c r="DE50" s="5"/>
+      <c r="DF50" s="5"/>
+      <c r="DG50" s="5"/>
+      <c r="DH50" s="5"/>
+      <c r="DI50" s="5"/>
+      <c r="DJ50" s="5"/>
+      <c r="DK50" s="5"/>
+      <c r="DL50" s="5"/>
+      <c r="DM50" s="5"/>
+      <c r="DN50" s="5"/>
+      <c r="DO50" s="5"/>
+      <c r="DP50" s="5"/>
+      <c r="DQ50" s="5"/>
+      <c r="DR50" s="5"/>
+      <c r="DS50" s="5"/>
+      <c r="DT50" s="5"/>
+      <c r="DU50" s="5"/>
+      <c r="DV50" s="5"/>
+      <c r="DW50" s="5"/>
+      <c r="DX50" s="5"/>
+      <c r="DY50" s="5"/>
+      <c r="DZ50" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:130">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="Q51" s="5"/>
+      <c r="AG51" s="5"/>
+      <c r="AX51" s="5"/>
+      <c r="BM51" s="6"/>
+      <c r="CB51" s="5"/>
+      <c r="CS51" s="5"/>
+      <c r="DI51" s="5"/>
+      <c r="DZ51" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:130">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q52" s="5"/>
+      <c r="AG52" s="5"/>
+      <c r="AX52" s="5"/>
+      <c r="BM52" s="6"/>
+      <c r="CB52" s="5"/>
+      <c r="CS52" s="5"/>
+      <c r="DI52" s="5"/>
+      <c r="DZ52" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:130">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="Q53" s="5"/>
+      <c r="AG53" s="5"/>
+      <c r="AX53" s="5"/>
+      <c r="BM53" s="6"/>
+      <c r="CB53" s="5"/>
+      <c r="CS53" s="5"/>
+      <c r="DI53" s="5"/>
+      <c r="DZ53" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:130">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="Q54" s="5"/>
+      <c r="AG54" s="5"/>
+      <c r="AX54" s="5"/>
+      <c r="BM54" s="6"/>
+      <c r="CB54" s="5"/>
+      <c r="CS54" s="5"/>
+      <c r="DI54" s="5"/>
+      <c r="DZ54" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:130">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="Q55" s="5"/>
+      <c r="AG55" s="5"/>
+      <c r="AX55" s="5"/>
+      <c r="BM55" s="6"/>
+      <c r="CB55" s="5"/>
+      <c r="CS55" s="5"/>
+      <c r="DI55" s="5"/>
+      <c r="DZ55" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:130">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="Q56" s="5"/>
+      <c r="AG56" s="5"/>
+      <c r="AX56" s="5"/>
+      <c r="BM56" s="6"/>
+      <c r="CB56" s="5"/>
+      <c r="CS56" s="5"/>
+      <c r="DI56" s="5"/>
+      <c r="DZ56" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:130">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="Q57" s="5"/>
+      <c r="AG57" s="5"/>
+      <c r="AX57" s="5"/>
+      <c r="BM57" s="6"/>
+      <c r="CB57" s="5"/>
+      <c r="CS57" s="5"/>
+      <c r="DI57" s="5"/>
+      <c r="DZ57" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:130">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="Q58" s="5"/>
+      <c r="AG58" s="5"/>
+      <c r="AX58" s="5"/>
+      <c r="BM58" s="6"/>
+      <c r="CB58" s="5"/>
+      <c r="CS58" s="5"/>
+      <c r="DI58" s="5"/>
+      <c r="DZ58" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:130">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="Q59" s="5"/>
+      <c r="AG59" s="5"/>
+      <c r="AX59" s="5"/>
+      <c r="BM59" s="6"/>
+      <c r="CB59" s="5"/>
+      <c r="CS59" s="5"/>
+      <c r="DI59" s="5"/>
+      <c r="DZ59" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:130">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="Q60" s="5"/>
+      <c r="AG60" s="5"/>
+      <c r="AX60" s="5"/>
+      <c r="BM60" s="6"/>
+      <c r="CB60" s="5"/>
+      <c r="CS60" s="5"/>
+      <c r="DI60" s="5"/>
+      <c r="DZ60" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:130">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="Q61" s="5"/>
+      <c r="AG61" s="5"/>
+      <c r="AX61" s="5"/>
+      <c r="BM61" s="6"/>
+      <c r="CB61" s="5"/>
+      <c r="CS61" s="5"/>
+      <c r="DI61" s="5"/>
+      <c r="DZ61" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:130">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="Q62" s="5"/>
+      <c r="AG62" s="5"/>
+      <c r="AX62" s="5"/>
+      <c r="BM62" s="6"/>
+      <c r="CB62" s="5"/>
+      <c r="CS62" s="5"/>
+      <c r="DI62" s="5"/>
+      <c r="DZ62" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:130">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="Q63" s="5"/>
+      <c r="AG63" s="5"/>
+      <c r="AX63" s="5"/>
+      <c r="BM63" s="6"/>
+      <c r="CB63" s="5"/>
+      <c r="CS63" s="5"/>
+      <c r="DI63" s="5"/>
+      <c r="DZ63" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:130">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="Q64" s="5"/>
+      <c r="AG64" s="5"/>
+      <c r="AX64" s="5"/>
+      <c r="BM64" s="6"/>
+      <c r="CB64" s="5"/>
+      <c r="CS64" s="5"/>
+      <c r="DI64" s="5"/>
+      <c r="DZ64" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:130">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="Q65" s="5"/>
+      <c r="AG65" s="5"/>
+      <c r="AX65" s="5"/>
+      <c r="BM65" s="6"/>
+      <c r="CB65" s="5"/>
+      <c r="CS65" s="5"/>
+      <c r="DI65" s="5"/>
+      <c r="DZ65" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:130">
+      <c r="B66" s="1">
+        <v>0</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2">
+        <v>3</v>
+      </c>
+      <c r="F66" s="2">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2">
+        <v>5</v>
+      </c>
+      <c r="H66" s="2">
+        <v>6</v>
+      </c>
+      <c r="I66" s="2">
+        <v>7</v>
+      </c>
+      <c r="J66" s="2">
+        <v>8</v>
+      </c>
+      <c r="K66" s="2">
+        <v>9</v>
+      </c>
+      <c r="L66" s="2">
+        <v>10</v>
+      </c>
+      <c r="M66" s="2">
+        <v>11</v>
+      </c>
+      <c r="N66" s="2">
+        <v>12</v>
+      </c>
+      <c r="O66" s="2">
+        <v>13</v>
+      </c>
+      <c r="P66" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>15</v>
+      </c>
+      <c r="R66" s="2">
+        <v>16</v>
+      </c>
+      <c r="S66" s="2">
+        <v>17</v>
+      </c>
+      <c r="T66" s="2">
+        <v>18</v>
+      </c>
+      <c r="U66" s="2">
+        <v>19</v>
+      </c>
+      <c r="V66" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y66" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z66" s="2">
+        <v>24</v>
+      </c>
+      <c r="AA66" s="2">
+        <v>25</v>
+      </c>
+      <c r="AB66" s="2">
+        <v>26</v>
+      </c>
+      <c r="AC66" s="2">
+        <v>27</v>
+      </c>
+      <c r="AD66" s="2">
+        <v>28</v>
+      </c>
+      <c r="AE66" s="2">
+        <v>29</v>
+      </c>
+      <c r="AF66" s="2">
+        <v>30</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>31</v>
+      </c>
+      <c r="AH66" s="2">
+        <v>32</v>
+      </c>
+      <c r="AI66" s="2">
+        <v>33</v>
+      </c>
+      <c r="AJ66" s="2">
+        <v>34</v>
+      </c>
+      <c r="AK66" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL66" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM66" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN66" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO66" s="2">
+        <v>39</v>
+      </c>
+      <c r="AP66" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ66" s="2">
+        <v>41</v>
+      </c>
+      <c r="AR66" s="2">
+        <v>42</v>
+      </c>
+      <c r="AS66" s="2">
+        <v>43</v>
+      </c>
+      <c r="AT66" s="2">
+        <v>44</v>
+      </c>
+      <c r="AU66" s="2">
+        <v>45</v>
+      </c>
+      <c r="AV66" s="2">
+        <v>46</v>
+      </c>
+      <c r="AW66" s="2">
+        <v>47</v>
+      </c>
+      <c r="AX66" s="3">
+        <v>48</v>
+      </c>
+      <c r="AY66" s="2">
+        <v>49</v>
+      </c>
+      <c r="AZ66" s="2">
+        <v>50</v>
+      </c>
+      <c r="BA66" s="2">
+        <v>51</v>
+      </c>
+      <c r="BB66" s="2">
+        <v>52</v>
+      </c>
+      <c r="BC66" s="2">
+        <v>53</v>
+      </c>
+      <c r="BD66" s="2">
+        <v>54</v>
+      </c>
+      <c r="BE66" s="2">
+        <v>55</v>
+      </c>
+      <c r="BF66" s="2">
+        <v>56</v>
+      </c>
+      <c r="BG66" s="2">
+        <v>57</v>
+      </c>
+      <c r="BH66" s="2">
+        <v>58</v>
+      </c>
+      <c r="BI66" s="2">
+        <v>59</v>
+      </c>
+      <c r="BJ66" s="2">
+        <v>60</v>
+      </c>
+      <c r="BK66" s="2">
+        <v>61</v>
+      </c>
+      <c r="BL66" s="2">
+        <v>62</v>
+      </c>
+      <c r="BM66" s="3">
+        <v>63</v>
+      </c>
+      <c r="BN66" s="2">
+        <v>64</v>
+      </c>
+      <c r="BO66" s="2">
+        <v>65</v>
+      </c>
+      <c r="BP66" s="2">
+        <v>66</v>
+      </c>
+      <c r="BQ66" s="2">
+        <v>67</v>
+      </c>
+      <c r="BR66" s="2">
+        <v>68</v>
+      </c>
+      <c r="BS66" s="2">
+        <v>69</v>
+      </c>
+      <c r="BT66" s="2">
+        <v>70</v>
+      </c>
+      <c r="BU66" s="2">
+        <v>71</v>
+      </c>
+      <c r="BV66" s="2">
+        <v>72</v>
+      </c>
+      <c r="BW66" s="2">
+        <v>73</v>
+      </c>
+      <c r="BX66" s="2">
+        <v>74</v>
+      </c>
+      <c r="BY66" s="2">
+        <v>75</v>
+      </c>
+      <c r="BZ66" s="2">
+        <v>76</v>
+      </c>
+      <c r="CA66" s="2">
+        <v>77</v>
+      </c>
+      <c r="CB66" s="3">
+        <v>78</v>
+      </c>
+      <c r="CC66" s="2">
+        <v>79</v>
+      </c>
+      <c r="CD66" s="2">
+        <v>80</v>
+      </c>
+      <c r="CE66" s="2">
+        <v>81</v>
+      </c>
+      <c r="CF66" s="2">
+        <v>82</v>
+      </c>
+      <c r="CG66" s="2">
+        <v>83</v>
+      </c>
+      <c r="CH66" s="2">
+        <v>84</v>
+      </c>
+      <c r="CI66" s="2">
+        <v>85</v>
+      </c>
+      <c r="CJ66" s="2">
+        <v>86</v>
+      </c>
+      <c r="CK66" s="2">
+        <v>87</v>
+      </c>
+      <c r="CL66" s="2">
+        <v>88</v>
+      </c>
+      <c r="CM66" s="2">
+        <v>89</v>
+      </c>
+      <c r="CN66" s="2">
+        <v>90</v>
+      </c>
+      <c r="CO66" s="2">
+        <v>91</v>
+      </c>
+      <c r="CP66" s="2">
+        <v>92</v>
+      </c>
+      <c r="CQ66" s="2">
+        <v>93</v>
+      </c>
+      <c r="CR66" s="2">
+        <v>94</v>
+      </c>
+      <c r="CS66" s="3">
+        <v>95</v>
+      </c>
+      <c r="CT66" s="2">
+        <v>96</v>
+      </c>
+      <c r="CU66" s="2">
+        <v>97</v>
+      </c>
+      <c r="CV66" s="2">
+        <v>98</v>
+      </c>
+      <c r="CW66" s="2">
+        <v>99</v>
+      </c>
+      <c r="CX66" s="2">
+        <v>100</v>
+      </c>
+      <c r="CY66" s="2">
+        <v>101</v>
+      </c>
+      <c r="CZ66" s="2">
+        <v>102</v>
+      </c>
+      <c r="DA66" s="2">
+        <v>103</v>
+      </c>
+      <c r="DB66" s="2">
+        <v>104</v>
+      </c>
+      <c r="DC66" s="2">
+        <v>105</v>
+      </c>
+      <c r="DD66" s="2">
+        <v>106</v>
+      </c>
+      <c r="DE66" s="2">
+        <v>107</v>
+      </c>
+      <c r="DF66" s="2">
+        <v>108</v>
+      </c>
+      <c r="DG66" s="2">
+        <v>109</v>
+      </c>
+      <c r="DH66" s="2">
+        <v>110</v>
+      </c>
+      <c r="DI66" s="3">
+        <v>111</v>
+      </c>
+      <c r="DJ66" s="2">
+        <v>112</v>
+      </c>
+      <c r="DK66" s="2">
+        <v>113</v>
+      </c>
+      <c r="DL66" s="2">
+        <v>114</v>
+      </c>
+      <c r="DM66" s="2">
+        <v>115</v>
+      </c>
+      <c r="DN66" s="2">
+        <v>116</v>
+      </c>
+      <c r="DO66" s="2">
+        <v>117</v>
+      </c>
+      <c r="DP66" s="2">
+        <v>118</v>
+      </c>
+      <c r="DQ66" s="2">
+        <v>119</v>
+      </c>
+      <c r="DR66" s="2">
+        <v>120</v>
+      </c>
+      <c r="DS66" s="2">
+        <v>121</v>
+      </c>
+      <c r="DT66" s="2">
+        <v>122</v>
+      </c>
+      <c r="DU66" s="2">
+        <v>123</v>
+      </c>
+      <c r="DV66" s="2">
+        <v>124</v>
+      </c>
+      <c r="DW66" s="2">
+        <v>125</v>
+      </c>
+      <c r="DX66" s="2">
+        <v>126</v>
+      </c>
+      <c r="DY66" s="2">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>